--- a/flutter_application_1/101_Okey_Seviye_ve_Ekonomi_Kurallari_Detayli.xlsx
+++ b/flutter_application_1/101_Okey_Seviye_ve_Ekonomi_Kurallari_Detayli.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d4b3de4e1ba46f8a/Desktop/101/101/flutter_application_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="613" documentId="8_{54D426F1-302D-4283-AE4B-BC8EED53E0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA77D3B7-655D-49C8-B086-5D0FE4435B75}"/>
+  <xr:revisionPtr revIDLastSave="615" documentId="8_{54D426F1-302D-4283-AE4B-BC8EED53E0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D48180C1-0A4E-4BCC-A51E-549B4FC2A8C6}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-975" windowWidth="29040" windowHeight="15720" xr2:uid="{072EF657-EB38-44E9-84FE-A4B54D9F5AF3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{072EF657-EB38-44E9-84FE-A4B54D9F5AF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Masa Seviye Kilitleri" sheetId="7" r:id="rId1"/>
@@ -21,21 +21,10 @@
     <sheet name="Seviye Gereksinimleri" sheetId="2" r:id="rId6"/>
     <sheet name="Altın Ekonomisi" sheetId="1" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -45,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="252">
   <si>
     <t>Kural</t>
   </si>
@@ -86,9 +75,6 @@
     <t>Örnek</t>
   </si>
   <si>
-    <t>Seviye 9'da 40/50 XP olan oyuncu 30 XP alınca Seviye 10 ve 20/50 XP olur.</t>
-  </si>
-  <si>
     <t>Oyun Türü</t>
   </si>
   <si>
@@ -104,9 +90,6 @@
     <t>Eli Bitirme</t>
   </si>
   <si>
-    <t>Tüm Başarılarla Toplam</t>
-  </si>
-  <si>
     <t>Hemen Oyna</t>
   </si>
   <si>
@@ -374,18 +357,6 @@
     <t>30 XP dolunca Seviye 3</t>
   </si>
   <si>
-    <t>30 XP dolunca Seviye 4</t>
-  </si>
-  <si>
-    <t>50 XP dolunca Seviye 6</t>
-  </si>
-  <si>
-    <t>50 XP dolunca Seviye 7</t>
-  </si>
-  <si>
-    <t>50 XP dolunca Seviye 8</t>
-  </si>
-  <si>
     <t>MAX</t>
   </si>
   <si>
@@ -398,9 +369,6 @@
     <t>Başlangıç bakiyesi</t>
   </si>
   <si>
-    <t>Varsayılan hesap bakiyesi</t>
-  </si>
-  <si>
     <t>Hemen Oyna galibiyeti</t>
   </si>
   <si>
@@ -440,9 +408,6 @@
     <t>Yeni oyuncu Seviye 0 - Beginner ve 0/30 XP ile başlar.</t>
   </si>
   <si>
-    <t>Seviye 3'te 20/30 XP bulunan oyuncu 30 XP kazanırsa Seviye 4 ve 20/50 XP olur.</t>
-  </si>
-  <si>
     <t>0-2</t>
   </si>
   <si>
@@ -780,6 +745,51 @@
   </si>
   <si>
     <t>25. seviyede açılır</t>
+  </si>
+  <si>
+    <t>Seviye, XP, altın ve oyuncu istatistikleri cihazda kalıcı olarak saklanır.</t>
+  </si>
+  <si>
+    <t>Seviye 3'te 20/50 XP olan oyuncu 40 XP alınca Seviye 4 ve 10/50 XP olur.</t>
+  </si>
+  <si>
+    <t>1. Turda Tüm Başarılarla Toplam</t>
+  </si>
+  <si>
+    <t>Tur galibiyeti bonusu</t>
+  </si>
+  <si>
+    <t>+10 x (tur no - 1)</t>
+  </si>
+  <si>
+    <t>En çok +200 XP</t>
+  </si>
+  <si>
+    <t>+10 XP / ek tur</t>
+  </si>
+  <si>
+    <t>Kazanana 2. turdan itibaren (tur no - 1) x 10 XP; en çok +200 XP.</t>
+  </si>
+  <si>
+    <t>50 XP dolunca Seviye 4</t>
+  </si>
+  <si>
+    <t>65 XP dolunca Seviye 6</t>
+  </si>
+  <si>
+    <t>65 XP dolunca Seviye 7</t>
+  </si>
+  <si>
+    <t>65 XP dolunca Seviye 8</t>
+  </si>
+  <si>
+    <t>Uygulamadaki varsayılan ve ilk geçiş bakiyesi</t>
+  </si>
+  <si>
+    <t>+50 x (tur no - 1)</t>
+  </si>
+  <si>
+    <t>Kazanana 2. turdan itibaren verilir; en çok +1.000 altın</t>
   </si>
 </sst>
 </file>
@@ -828,7 +838,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -838,6 +848,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -884,7 +900,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -904,6 +920,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1249,21 +1266,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B2" s="8">
         <v>0</v>
@@ -1272,12 +1289,12 @@
         <v>500</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="B3" s="8">
         <v>5</v>
@@ -1286,12 +1303,12 @@
         <v>1000</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B4" s="8">
         <v>15</v>
@@ -1300,12 +1317,12 @@
         <v>5000</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B5" s="8">
         <v>25</v>
@@ -1314,7 +1331,7 @@
         <v>10000</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -1344,7 +1361,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1384,7 +1401,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>131</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -1392,7 +1409,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -1402,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{820E5174-1592-4AC1-8090-9D2CF0B4A4B9}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.77734375" customWidth="1"/>
@@ -1410,29 +1427,29 @@
     <col min="6" max="6" width="25.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>19</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1">
         <v>30</v>
@@ -1452,7 +1469,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1">
         <v>30</v>
@@ -1472,7 +1489,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1">
         <v>35</v>
@@ -1492,7 +1509,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1">
         <v>50</v>
@@ -1508,6 +1525,20 @@
       </c>
       <c r="F5" s="1">
         <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9" t="s">
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -1517,7 +1548,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0656E643-CF5A-4AA5-AF4E-7DD32B524D4C}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.77734375" customWidth="1"/>
@@ -1527,10 +1558,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -1538,178 +1569,189 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>62</v>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -1729,21 +1771,21 @@
   <sheetData>
     <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1">
         <v>30</v>
@@ -1751,21 +1793,21 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C3" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" s="1">
         <v>50</v>
@@ -1773,21 +1815,21 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C5" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C6" s="1">
         <v>75</v>
@@ -1795,10 +1837,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C7" s="1">
         <v>75</v>
@@ -1806,10 +1848,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C8" s="1">
         <v>100</v>
@@ -1817,10 +1859,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C9" s="1">
         <v>100</v>
@@ -1828,10 +1870,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C10" s="1">
         <v>130</v>
@@ -1839,10 +1881,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C11" s="1">
         <v>130</v>
@@ -1850,10 +1892,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C12" s="1">
         <v>170</v>
@@ -1861,10 +1903,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C13" s="1">
         <v>170</v>
@@ -1872,10 +1914,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C14" s="1">
         <v>170</v>
@@ -1883,10 +1925,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C15" s="1">
         <v>220</v>
@@ -1894,10 +1936,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C16" s="1">
         <v>220</v>
@@ -1905,10 +1947,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C17" s="1">
         <v>220</v>
@@ -1916,10 +1958,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C18" s="1">
         <v>280</v>
@@ -1927,10 +1969,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C19" s="1">
         <v>280</v>
@@ -1938,10 +1980,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C20" s="1">
         <v>280</v>
@@ -1949,10 +1991,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C21" s="1">
         <v>350</v>
@@ -1960,10 +2002,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C22" s="1">
         <v>350</v>
@@ -1971,10 +2013,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C23" s="1">
         <v>350</v>
@@ -1982,10 +2024,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C24" s="1">
         <v>450</v>
@@ -1993,10 +2035,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C25" s="1">
         <v>450</v>
@@ -2004,13 +2046,13 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2032,19 +2074,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2052,7 +2094,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C2" s="4">
         <v>30</v>
@@ -2061,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -2069,7 +2111,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" s="4">
         <v>30</v>
@@ -2078,7 +2120,7 @@
         <v>30</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -2086,7 +2128,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C4" s="4">
         <v>30</v>
@@ -2095,7 +2137,7 @@
         <v>60</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2103,16 +2145,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C5" s="4">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D5" s="4">
         <v>90</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>109</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2120,16 +2162,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C6" s="4">
         <v>50</v>
       </c>
       <c r="D6" s="4">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -2137,16 +2179,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C7" s="4">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D7" s="4">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>110</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2154,16 +2196,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C8" s="4">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D8" s="4">
-        <v>220</v>
+        <v>255</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>111</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -2171,16 +2213,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C9" s="4">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D9" s="4">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>112</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -2188,16 +2230,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C10" s="4">
         <v>75</v>
       </c>
       <c r="D10" s="4">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -2205,16 +2247,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C11" s="4">
         <v>75</v>
       </c>
       <c r="D11" s="4">
-        <v>395</v>
+        <v>460</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -2222,16 +2264,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C12" s="4">
         <v>75</v>
       </c>
       <c r="D12" s="4">
-        <v>470</v>
+        <v>535</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -2239,16 +2281,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C13" s="4">
         <v>75</v>
       </c>
       <c r="D13" s="4">
-        <v>545</v>
+        <v>610</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -2256,16 +2298,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C14" s="4">
         <v>75</v>
       </c>
       <c r="D14" s="4">
-        <v>620</v>
+        <v>685</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -2273,16 +2315,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C15" s="4">
         <v>100</v>
       </c>
       <c r="D15" s="4">
-        <v>695</v>
+        <v>760</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -2290,16 +2332,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C16" s="4">
         <v>100</v>
       </c>
       <c r="D16" s="4">
-        <v>795</v>
+        <v>860</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -2307,16 +2349,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C17" s="4">
         <v>100</v>
       </c>
       <c r="D17" s="4">
-        <v>895</v>
+        <v>960</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -2324,16 +2366,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C18" s="4">
         <v>100</v>
       </c>
       <c r="D18" s="4">
-        <v>995</v>
+        <v>1060</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -2341,16 +2383,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C19" s="4">
         <v>100</v>
       </c>
       <c r="D19" s="4">
-        <v>1095</v>
+        <v>1160</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -2358,16 +2400,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C20" s="4">
         <v>100</v>
       </c>
       <c r="D20" s="4">
-        <v>1195</v>
+        <v>1260</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -2375,16 +2417,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C21" s="4">
         <v>100</v>
       </c>
       <c r="D21" s="4">
-        <v>1295</v>
+        <v>1360</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -2392,16 +2434,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C22" s="4">
         <v>130</v>
       </c>
       <c r="D22" s="4">
-        <v>1395</v>
+        <v>1460</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -2409,16 +2451,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C23" s="4">
         <v>130</v>
       </c>
       <c r="D23" s="4">
-        <v>1525</v>
+        <v>1590</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -2426,16 +2468,16 @@
         <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C24" s="4">
         <v>130</v>
       </c>
       <c r="D24" s="4">
-        <v>1655</v>
+        <v>1720</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -2443,16 +2485,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C25" s="4">
         <v>130</v>
       </c>
       <c r="D25" s="4">
-        <v>1785</v>
+        <v>1850</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -2460,16 +2502,16 @@
         <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C26" s="4">
         <v>130</v>
       </c>
       <c r="D26" s="4">
-        <v>1915</v>
+        <v>1980</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -2477,16 +2519,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C27" s="4">
         <v>130</v>
       </c>
       <c r="D27" s="4">
-        <v>2045</v>
+        <v>2110</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -2494,16 +2536,16 @@
         <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C28" s="4">
         <v>130</v>
       </c>
       <c r="D28" s="4">
-        <v>2175</v>
+        <v>2240</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -2511,16 +2553,16 @@
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C29" s="4">
         <v>130</v>
       </c>
       <c r="D29" s="4">
-        <v>2305</v>
+        <v>2370</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -2528,16 +2570,16 @@
         <v>28</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C30" s="4">
         <v>130</v>
       </c>
       <c r="D30" s="4">
-        <v>2435</v>
+        <v>2500</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -2545,16 +2587,16 @@
         <v>29</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C31" s="4">
         <v>130</v>
       </c>
       <c r="D31" s="4">
-        <v>2565</v>
+        <v>2630</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -2562,16 +2604,16 @@
         <v>30</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C32" s="4">
         <v>170</v>
       </c>
       <c r="D32" s="4">
-        <v>2695</v>
+        <v>2760</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -2579,16 +2621,16 @@
         <v>31</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C33" s="4">
         <v>170</v>
       </c>
       <c r="D33" s="4">
-        <v>2865</v>
+        <v>2930</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -2596,16 +2638,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C34" s="4">
         <v>170</v>
       </c>
       <c r="D34" s="4">
-        <v>3035</v>
+        <v>3100</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -2613,16 +2655,16 @@
         <v>33</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C35" s="4">
         <v>170</v>
       </c>
       <c r="D35" s="4">
-        <v>3205</v>
+        <v>3270</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -2630,16 +2672,16 @@
         <v>34</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C36" s="4">
         <v>170</v>
       </c>
       <c r="D36" s="4">
-        <v>3375</v>
+        <v>3440</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -2647,16 +2689,16 @@
         <v>35</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C37" s="4">
         <v>170</v>
       </c>
       <c r="D37" s="4">
-        <v>3545</v>
+        <v>3610</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -2664,16 +2706,16 @@
         <v>36</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C38" s="4">
         <v>170</v>
       </c>
       <c r="D38" s="4">
-        <v>3715</v>
+        <v>3780</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -2681,16 +2723,16 @@
         <v>37</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C39" s="4">
         <v>170</v>
       </c>
       <c r="D39" s="4">
-        <v>3885</v>
+        <v>3950</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -2698,16 +2740,16 @@
         <v>38</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C40" s="4">
         <v>170</v>
       </c>
       <c r="D40" s="4">
-        <v>4055</v>
+        <v>4120</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -2715,16 +2757,16 @@
         <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C41" s="4">
         <v>170</v>
       </c>
       <c r="D41" s="4">
-        <v>4225</v>
+        <v>4290</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -2732,16 +2774,16 @@
         <v>40</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C42" s="4">
         <v>170</v>
       </c>
       <c r="D42" s="4">
-        <v>4395</v>
+        <v>4460</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -2749,16 +2791,16 @@
         <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C43" s="4">
         <v>170</v>
       </c>
       <c r="D43" s="4">
-        <v>4565</v>
+        <v>4630</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -2766,16 +2808,16 @@
         <v>42</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C44" s="4">
         <v>170</v>
       </c>
       <c r="D44" s="4">
-        <v>4735</v>
+        <v>4800</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -2783,16 +2825,16 @@
         <v>43</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C45" s="4">
         <v>170</v>
       </c>
       <c r="D45" s="4">
-        <v>4905</v>
+        <v>4970</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -2800,16 +2842,16 @@
         <v>44</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C46" s="4">
         <v>170</v>
       </c>
       <c r="D46" s="4">
-        <v>5075</v>
+        <v>5140</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -2817,16 +2859,16 @@
         <v>45</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C47" s="4">
         <v>220</v>
       </c>
       <c r="D47" s="4">
-        <v>5245</v>
+        <v>5310</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -2834,16 +2876,16 @@
         <v>46</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C48" s="4">
         <v>220</v>
       </c>
       <c r="D48" s="4">
-        <v>5465</v>
+        <v>5530</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -2851,16 +2893,16 @@
         <v>47</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C49" s="4">
         <v>220</v>
       </c>
       <c r="D49" s="4">
-        <v>5685</v>
+        <v>5750</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -2868,16 +2910,16 @@
         <v>48</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C50" s="4">
         <v>220</v>
       </c>
       <c r="D50" s="4">
-        <v>5905</v>
+        <v>5970</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -2885,16 +2927,16 @@
         <v>49</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C51" s="4">
         <v>220</v>
       </c>
       <c r="D51" s="4">
-        <v>6125</v>
+        <v>6190</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -2902,16 +2944,16 @@
         <v>50</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C52" s="4">
         <v>220</v>
       </c>
       <c r="D52" s="4">
-        <v>6345</v>
+        <v>6410</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -2919,16 +2961,16 @@
         <v>51</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C53" s="4">
         <v>220</v>
       </c>
       <c r="D53" s="4">
-        <v>6565</v>
+        <v>6630</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -2936,16 +2978,16 @@
         <v>52</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C54" s="4">
         <v>220</v>
       </c>
       <c r="D54" s="4">
-        <v>6785</v>
+        <v>6850</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -2953,16 +2995,16 @@
         <v>53</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C55" s="4">
         <v>220</v>
       </c>
       <c r="D55" s="4">
-        <v>7005</v>
+        <v>7070</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -2970,16 +3012,16 @@
         <v>54</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C56" s="4">
         <v>220</v>
       </c>
       <c r="D56" s="4">
-        <v>7225</v>
+        <v>7290</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -2987,16 +3029,16 @@
         <v>55</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C57" s="4">
         <v>220</v>
       </c>
       <c r="D57" s="4">
-        <v>7445</v>
+        <v>7510</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -3004,16 +3046,16 @@
         <v>56</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C58" s="4">
         <v>220</v>
       </c>
       <c r="D58" s="4">
-        <v>7665</v>
+        <v>7730</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -3021,16 +3063,16 @@
         <v>57</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C59" s="4">
         <v>220</v>
       </c>
       <c r="D59" s="4">
-        <v>7885</v>
+        <v>7950</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -3038,16 +3080,16 @@
         <v>58</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C60" s="4">
         <v>220</v>
       </c>
       <c r="D60" s="4">
-        <v>8105</v>
+        <v>8170</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -3055,16 +3097,16 @@
         <v>59</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C61" s="4">
         <v>220</v>
       </c>
       <c r="D61" s="4">
-        <v>8325</v>
+        <v>8390</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -3072,16 +3114,16 @@
         <v>60</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C62" s="4">
         <v>280</v>
       </c>
       <c r="D62" s="4">
-        <v>8545</v>
+        <v>8610</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -3089,16 +3131,16 @@
         <v>61</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C63" s="4">
         <v>280</v>
       </c>
       <c r="D63" s="4">
-        <v>8825</v>
+        <v>8890</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -3106,16 +3148,16 @@
         <v>62</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C64" s="4">
         <v>280</v>
       </c>
       <c r="D64" s="4">
-        <v>9105</v>
+        <v>9170</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -3123,16 +3165,16 @@
         <v>63</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C65" s="4">
         <v>280</v>
       </c>
       <c r="D65" s="4">
-        <v>9385</v>
+        <v>9450</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -3140,16 +3182,16 @@
         <v>64</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C66" s="4">
         <v>280</v>
       </c>
       <c r="D66" s="4">
-        <v>9665</v>
+        <v>9730</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -3157,16 +3199,16 @@
         <v>65</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C67" s="4">
         <v>280</v>
       </c>
       <c r="D67" s="4">
-        <v>9945</v>
+        <v>10010</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -3174,16 +3216,16 @@
         <v>66</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C68" s="4">
         <v>280</v>
       </c>
       <c r="D68" s="4">
-        <v>10225</v>
+        <v>10290</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -3191,16 +3233,16 @@
         <v>67</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C69" s="4">
         <v>280</v>
       </c>
       <c r="D69" s="4">
-        <v>10505</v>
+        <v>10570</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -3208,16 +3250,16 @@
         <v>68</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C70" s="4">
         <v>280</v>
       </c>
       <c r="D70" s="4">
-        <v>10785</v>
+        <v>10850</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -3225,16 +3267,16 @@
         <v>69</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C71" s="4">
         <v>280</v>
       </c>
       <c r="D71" s="4">
-        <v>11065</v>
+        <v>11130</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -3242,16 +3284,16 @@
         <v>70</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C72" s="4">
         <v>280</v>
       </c>
       <c r="D72" s="4">
-        <v>11345</v>
+        <v>11410</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -3259,16 +3301,16 @@
         <v>71</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C73" s="4">
         <v>280</v>
       </c>
       <c r="D73" s="4">
-        <v>11625</v>
+        <v>11690</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -3276,16 +3318,16 @@
         <v>72</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C74" s="4">
         <v>280</v>
       </c>
       <c r="D74" s="4">
-        <v>11905</v>
+        <v>11970</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -3293,16 +3335,16 @@
         <v>73</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C75" s="4">
         <v>280</v>
       </c>
       <c r="D75" s="4">
-        <v>12185</v>
+        <v>12250</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
@@ -3310,16 +3352,16 @@
         <v>74</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C76" s="4">
         <v>280</v>
       </c>
       <c r="D76" s="4">
-        <v>12465</v>
+        <v>12530</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -3327,16 +3369,16 @@
         <v>75</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C77" s="4">
         <v>350</v>
       </c>
       <c r="D77" s="4">
-        <v>12745</v>
+        <v>12810</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -3344,16 +3386,16 @@
         <v>76</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C78" s="4">
         <v>350</v>
       </c>
       <c r="D78" s="4">
-        <v>13095</v>
+        <v>13160</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -3361,16 +3403,16 @@
         <v>77</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C79" s="4">
         <v>350</v>
       </c>
       <c r="D79" s="4">
-        <v>13445</v>
+        <v>13510</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -3378,16 +3420,16 @@
         <v>78</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C80" s="4">
         <v>350</v>
       </c>
       <c r="D80" s="4">
-        <v>13795</v>
+        <v>13860</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -3395,16 +3437,16 @@
         <v>79</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C81" s="4">
         <v>350</v>
       </c>
       <c r="D81" s="4">
-        <v>14145</v>
+        <v>14210</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -3412,16 +3454,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C82" s="4">
         <v>350</v>
       </c>
       <c r="D82" s="4">
-        <v>14495</v>
+        <v>14560</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -3429,16 +3471,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C83" s="4">
         <v>350</v>
       </c>
       <c r="D83" s="4">
-        <v>14845</v>
+        <v>14910</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -3446,16 +3488,16 @@
         <v>82</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C84" s="4">
         <v>350</v>
       </c>
       <c r="D84" s="4">
-        <v>15195</v>
+        <v>15260</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -3463,16 +3505,16 @@
         <v>83</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C85" s="4">
         <v>350</v>
       </c>
       <c r="D85" s="4">
-        <v>15545</v>
+        <v>15610</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -3480,16 +3522,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C86" s="4">
         <v>350</v>
       </c>
       <c r="D86" s="4">
-        <v>15895</v>
+        <v>15960</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -3497,16 +3539,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C87" s="4">
         <v>350</v>
       </c>
       <c r="D87" s="4">
-        <v>16245</v>
+        <v>16310</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -3514,16 +3556,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C88" s="4">
         <v>350</v>
       </c>
       <c r="D88" s="4">
-        <v>16595</v>
+        <v>16660</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -3531,16 +3573,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C89" s="4">
         <v>350</v>
       </c>
       <c r="D89" s="4">
-        <v>16945</v>
+        <v>17010</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -3548,16 +3590,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C90" s="4">
         <v>350</v>
       </c>
       <c r="D90" s="4">
-        <v>17295</v>
+        <v>17360</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -3565,16 +3607,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C91" s="4">
         <v>350</v>
       </c>
       <c r="D91" s="4">
-        <v>17645</v>
+        <v>17710</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -3582,16 +3624,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C92" s="4">
         <v>450</v>
       </c>
       <c r="D92" s="4">
-        <v>17995</v>
+        <v>18060</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -3599,16 +3641,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C93" s="4">
         <v>450</v>
       </c>
       <c r="D93" s="4">
-        <v>18445</v>
+        <v>18510</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -3616,16 +3658,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C94" s="4">
         <v>450</v>
       </c>
       <c r="D94" s="4">
-        <v>18895</v>
+        <v>18960</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -3633,16 +3675,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C95" s="4">
         <v>450</v>
       </c>
       <c r="D95" s="4">
-        <v>19345</v>
+        <v>19410</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -3650,16 +3692,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C96" s="4">
         <v>450</v>
       </c>
       <c r="D96" s="4">
-        <v>19795</v>
+        <v>19860</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
@@ -3667,16 +3709,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C97" s="4">
         <v>450</v>
       </c>
       <c r="D97" s="4">
-        <v>20245</v>
+        <v>20310</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
@@ -3684,16 +3726,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C98" s="4">
         <v>450</v>
       </c>
       <c r="D98" s="4">
-        <v>20695</v>
+        <v>20760</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
@@ -3701,16 +3743,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C99" s="4">
         <v>450</v>
       </c>
       <c r="D99" s="4">
-        <v>21145</v>
+        <v>21210</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -3718,16 +3760,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C100" s="4">
         <v>450</v>
       </c>
       <c r="D100" s="4">
-        <v>21595</v>
+        <v>21660</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -3735,13 +3777,13 @@
         <v>99</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D101" s="4">
-        <v>22045</v>
+        <v>22110</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>9</v>
@@ -3754,7 +3796,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33C58E83-49AD-43EC-A12E-130AD11BB45A}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.77734375" customWidth="1"/>
@@ -3764,10 +3806,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -3775,68 +3817,79 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B2" s="1">
-        <v>25600</v>
+        <v>100000</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B3" s="1">
         <v>150</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B4" s="1">
         <v>300</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
